--- a/data/final/comexstat/resumo_disponibilidade_comexstat.xlsx
+++ b/data/final/comexstat/resumo_disponibilidade_comexstat.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -464,19 +464,19 @@
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>35461</v>
+        <v>43861</v>
       </c>
       <c r="C2" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D2" t="n">
-        <v>356</v>
+        <v>80</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>3680971118</v>
+        <v>14429715267</v>
       </c>
       <c r="G2" t="n">
         <v>33157804370</v>
@@ -489,19 +489,19 @@
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>35461</v>
+        <v>43861</v>
       </c>
       <c r="C3" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D3" t="n">
-        <v>356</v>
+        <v>80</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>2588659779</v>
+        <v>17190165488</v>
       </c>
       <c r="G3" t="n">
         <v>25763862100</v>
@@ -514,19 +514,19 @@
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>35461</v>
+        <v>43861</v>
       </c>
       <c r="C4" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D4" t="n">
-        <v>356</v>
+        <v>80</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>1092311339</v>
+        <v>-2760450221</v>
       </c>
       <c r="G4" t="n">
         <v>7393942270</v>
@@ -539,19 +539,19 @@
         </is>
       </c>
       <c r="B5" s="1" t="n">
-        <v>35461</v>
+        <v>43861</v>
       </c>
       <c r="C5" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D5" t="n">
-        <v>356</v>
+        <v>80</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>6269630897</v>
+        <v>31619880755</v>
       </c>
       <c r="G5" t="n">
         <v>58921666470</v>
@@ -564,19 +564,19 @@
         </is>
       </c>
       <c r="B6" s="1" t="n">
-        <v>35461</v>
+        <v>43861</v>
       </c>
       <c r="C6" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D6" t="n">
-        <v>356</v>
+        <v>80</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>17370770826</v>
+        <v>46718273016</v>
       </c>
       <c r="G6" t="n">
         <v>77119199389</v>
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="B7" s="1" t="n">
-        <v>35461</v>
+        <v>43861</v>
       </c>
       <c r="C7" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D7" t="n">
-        <v>356</v>
+        <v>80</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>1569629726</v>
+        <v>12206525099</v>
       </c>
       <c r="G7" t="n">
         <v>14073182023</v>
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="B8" s="1" t="n">
-        <v>35461</v>
+        <v>43861</v>
       </c>
       <c r="C8" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D8" t="n">
-        <v>356</v>
+        <v>80</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>154149785</v>
+        <v>641249369</v>
       </c>
       <c r="G8" t="n">
         <v>1548184686</v>
@@ -639,19 +639,19 @@
         </is>
       </c>
       <c r="B9" s="1" t="n">
-        <v>35461</v>
+        <v>43861</v>
       </c>
       <c r="C9" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D9" t="n">
-        <v>356</v>
+        <v>80</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>7008789</v>
+        <v>11309879</v>
       </c>
       <c r="G9" t="n">
         <v>19241881</v>
@@ -664,22 +664,1022 @@
         </is>
       </c>
       <c r="B10" s="1" t="n">
-        <v>35461</v>
+        <v>43861</v>
       </c>
       <c r="C10" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D10" t="n">
-        <v>356</v>
+        <v>80</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>2749818353</v>
+        <v>17842724736</v>
       </c>
       <c r="G10" t="n">
         <v>27331288667</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>comex_ncm_02023000_carne_bovina_congelada_exportacoes_fob_usd</t>
+        </is>
+      </c>
+      <c r="B11" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="C11" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D11" t="n">
+        <v>80</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>500185177</v>
+      </c>
+      <c r="G11" t="n">
+        <v>967242706</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>comex_ncm_02023000_carne_bovina_congelada_exportacoes_kg</t>
+        </is>
+      </c>
+      <c r="B12" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="C12" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D12" t="n">
+        <v>80</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>103909023</v>
+      </c>
+      <c r="G12" t="n">
+        <v>162300453</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>comex_ncm_02023000_carne_bovina_congelada_importacoes_fob_usd</t>
+        </is>
+      </c>
+      <c r="B13" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="C13" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D13" t="n">
+        <v>80</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>9788257</v>
+      </c>
+      <c r="G13" t="n">
+        <v>9868969</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>comex_ncm_02023000_carne_bovina_congelada_importacoes_kg</t>
+        </is>
+      </c>
+      <c r="B14" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="C14" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D14" t="n">
+        <v>80</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1182973</v>
+      </c>
+      <c r="G14" t="n">
+        <v>942383</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>comex_ncm_09011110_cafe_nao_torrado_exportacoes_fob_usd</t>
+        </is>
+      </c>
+      <c r="B15" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="C15" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D15" t="n">
+        <v>80</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>357877575</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1094109253</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>comex_ncm_09011110_cafe_nao_torrado_exportacoes_kg</t>
+        </is>
+      </c>
+      <c r="B16" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="C16" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D16" t="n">
+        <v>80</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>163332129</v>
+      </c>
+      <c r="G16" t="n">
+        <v>206264157</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>comex_ncm_09011110_cafe_nao_torrado_importacoes_fob_usd</t>
+        </is>
+      </c>
+      <c r="B17" s="1" t="n">
+        <v>44043</v>
+      </c>
+      <c r="C17" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="D17" t="n">
+        <v>22</v>
+      </c>
+      <c r="E17" t="n">
+        <v>58</v>
+      </c>
+      <c r="F17" t="n">
+        <v>31418</v>
+      </c>
+      <c r="G17" t="n">
+        <v>6294</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>comex_ncm_09011110_cafe_nao_torrado_importacoes_kg</t>
+        </is>
+      </c>
+      <c r="B18" s="1" t="n">
+        <v>44043</v>
+      </c>
+      <c r="C18" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="D18" t="n">
+        <v>22</v>
+      </c>
+      <c r="E18" t="n">
+        <v>58</v>
+      </c>
+      <c r="F18" t="n">
+        <v>20000</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1560</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>comex_ncm_10059010_milho_em_grao_exportacoes_fob_usd</t>
+        </is>
+      </c>
+      <c r="B19" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="C19" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D19" t="n">
+        <v>80</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>349915062</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1002656682</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>comex_ncm_10059010_milho_em_grao_exportacoes_kg</t>
+        </is>
+      </c>
+      <c r="B20" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="C20" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D20" t="n">
+        <v>80</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2083530104</v>
+      </c>
+      <c r="G20" t="n">
+        <v>4653100189</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>comex_ncm_10059010_milho_em_grao_importacoes_fob_usd</t>
+        </is>
+      </c>
+      <c r="B21" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="C21" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D21" t="n">
+        <v>80</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>26216991</v>
+      </c>
+      <c r="G21" t="n">
+        <v>33273820</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>comex_ncm_10059010_milho_em_grao_importacoes_kg</t>
+        </is>
+      </c>
+      <c r="B22" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="C22" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D22" t="n">
+        <v>80</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>196178640</v>
+      </c>
+      <c r="G22" t="n">
+        <v>199281400</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>comex_ncm_12019000_soja_exceto_semeadura_exportacoes_fob_usd</t>
+        </is>
+      </c>
+      <c r="B23" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="C23" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D23" t="n">
+        <v>80</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>504774218</v>
+      </c>
+      <c r="G23" t="n">
+        <v>4410039153</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>comex_ncm_12019000_soja_exceto_semeadura_exportacoes_kg</t>
+        </is>
+      </c>
+      <c r="B24" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="C24" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D24" t="n">
+        <v>80</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1397018249</v>
+      </c>
+      <c r="G24" t="n">
+        <v>9808807495</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>comex_ncm_12019000_soja_exceto_semeadura_importacoes_fob_usd</t>
+        </is>
+      </c>
+      <c r="B25" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="C25" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D25" t="n">
+        <v>76</v>
+      </c>
+      <c r="E25" t="n">
+        <v>4</v>
+      </c>
+      <c r="F25" t="n">
+        <v>6305340</v>
+      </c>
+      <c r="G25" t="n">
+        <v>44621019</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>comex_ncm_12019000_soja_exceto_semeadura_importacoes_kg</t>
+        </is>
+      </c>
+      <c r="B26" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="C26" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D26" t="n">
+        <v>76</v>
+      </c>
+      <c r="E26" t="n">
+        <v>4</v>
+      </c>
+      <c r="F26" t="n">
+        <v>19690000</v>
+      </c>
+      <c r="G26" t="n">
+        <v>109088024</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>comex_ncm_17011400_acucares_cana_exportacoes_fob_usd</t>
+        </is>
+      </c>
+      <c r="B27" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="C27" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D27" t="n">
+        <v>80</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="n">
+        <v>395907378</v>
+      </c>
+      <c r="G27" t="n">
+        <v>753147930</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>comex_ncm_17011400_acucares_cana_exportacoes_kg</t>
+        </is>
+      </c>
+      <c r="B28" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="C28" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D28" t="n">
+        <v>80</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1403790404</v>
+      </c>
+      <c r="G28" t="n">
+        <v>2221291720</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>comex_ncm_17011400_acucares_cana_importacoes_fob_usd</t>
+        </is>
+      </c>
+      <c r="B29" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="C29" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D29" t="n">
+        <v>79</v>
+      </c>
+      <c r="E29" t="n">
+        <v>1</v>
+      </c>
+      <c r="F29" t="n">
+        <v>42579</v>
+      </c>
+      <c r="G29" t="n">
+        <v>170442</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>comex_ncm_17011400_acucares_cana_importacoes_kg</t>
+        </is>
+      </c>
+      <c r="B30" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="C30" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D30" t="n">
+        <v>79</v>
+      </c>
+      <c r="E30" t="n">
+        <v>1</v>
+      </c>
+      <c r="F30" t="n">
+        <v>41657</v>
+      </c>
+      <c r="G30" t="n">
+        <v>143344</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>comex_ncm_23040090_residuos_oleo_soja_exportacoes_fob_usd</t>
+        </is>
+      </c>
+      <c r="B31" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="C31" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D31" t="n">
+        <v>80</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" t="n">
+        <v>281324952</v>
+      </c>
+      <c r="G31" t="n">
+        <v>646488066</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>comex_ncm_23040090_residuos_oleo_soja_exportacoes_kg</t>
+        </is>
+      </c>
+      <c r="B32" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="C32" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D32" t="n">
+        <v>80</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" t="n">
+        <v>831821378</v>
+      </c>
+      <c r="G32" t="n">
+        <v>1790486389</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>comex_ncm_23040090_residuos_oleo_soja_importacoes_fob_usd</t>
+        </is>
+      </c>
+      <c r="B33" s="1" t="n">
+        <v>43890</v>
+      </c>
+      <c r="C33" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D33" t="n">
+        <v>5</v>
+      </c>
+      <c r="E33" t="n">
+        <v>75</v>
+      </c>
+      <c r="F33" t="n">
+        <v>2282</v>
+      </c>
+      <c r="G33" t="n">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>comex_ncm_23040090_residuos_oleo_soja_importacoes_kg</t>
+        </is>
+      </c>
+      <c r="B34" s="1" t="n">
+        <v>43890</v>
+      </c>
+      <c r="C34" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D34" t="n">
+        <v>5</v>
+      </c>
+      <c r="E34" t="n">
+        <v>75</v>
+      </c>
+      <c r="F34" t="n">
+        <v>2500</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>comex_ncm_26011100_minerio_ferro_nao_aglomerado_exportacoes_fob_usd</t>
+        </is>
+      </c>
+      <c r="B35" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="C35" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D35" t="n">
+        <v>80</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1627139024</v>
+      </c>
+      <c r="G35" t="n">
+        <v>2051566400</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>comex_ncm_26011100_minerio_ferro_nao_aglomerado_exportacoes_kg</t>
+        </is>
+      </c>
+      <c r="B36" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="C36" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D36" t="n">
+        <v>80</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" t="n">
+        <v>25418986258</v>
+      </c>
+      <c r="G36" t="n">
+        <v>34406447895</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>comex_ncm_26011100_minerio_ferro_nao_aglomerado_importacoes_fob_usd</t>
+        </is>
+      </c>
+      <c r="B37" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="C37" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D37" t="n">
+        <v>66</v>
+      </c>
+      <c r="E37" t="n">
+        <v>14</v>
+      </c>
+      <c r="F37" t="n">
+        <v>6207</v>
+      </c>
+      <c r="G37" t="n">
+        <v>6950029</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>comex_ncm_26011100_minerio_ferro_nao_aglomerado_importacoes_kg</t>
+        </is>
+      </c>
+      <c r="B38" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="C38" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D38" t="n">
+        <v>66</v>
+      </c>
+      <c r="E38" t="n">
+        <v>14</v>
+      </c>
+      <c r="F38" t="n">
+        <v>7200</v>
+      </c>
+      <c r="G38" t="n">
+        <v>78331372</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>comex_ncm_27090010_oleos_brutos_petroleo_exportacoes_fob_usd</t>
+        </is>
+      </c>
+      <c r="B39" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="C39" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D39" t="n">
+        <v>80</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" t="n">
+        <v>1707992437</v>
+      </c>
+      <c r="G39" t="n">
+        <v>4828191084</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>comex_ncm_27090010_oleos_brutos_petroleo_exportacoes_kg</t>
+        </is>
+      </c>
+      <c r="B40" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="C40" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D40" t="n">
+        <v>80</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" t="n">
+        <v>4221906804</v>
+      </c>
+      <c r="G40" t="n">
+        <v>8379911835</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>comex_ncm_27090010_oleos_brutos_petroleo_importacoes_fob_usd</t>
+        </is>
+      </c>
+      <c r="B41" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="C41" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D41" t="n">
+        <v>80</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" t="n">
+        <v>207990371</v>
+      </c>
+      <c r="G41" t="n">
+        <v>547298813</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>comex_ncm_27090010_oleos_brutos_petroleo_importacoes_kg</t>
+        </is>
+      </c>
+      <c r="B42" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="C42" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D42" t="n">
+        <v>80</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" t="n">
+        <v>432290309</v>
+      </c>
+      <c r="G42" t="n">
+        <v>797225701</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>comex_ncm_27101922_fuel_oil_exportacoes_fob_usd</t>
+        </is>
+      </c>
+      <c r="B43" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="C43" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D43" t="n">
+        <v>80</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" t="n">
+        <v>401663716</v>
+      </c>
+      <c r="G43" t="n">
+        <v>893582419</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>comex_ncm_27101922_fuel_oil_exportacoes_kg</t>
+        </is>
+      </c>
+      <c r="B44" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="C44" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D44" t="n">
+        <v>80</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="n">
+        <v>955961547</v>
+      </c>
+      <c r="G44" t="n">
+        <v>1438094595</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>comex_ncm_27101922_fuel_oil_importacoes_fob_usd</t>
+        </is>
+      </c>
+      <c r="B45" s="1" t="n">
+        <v>44196</v>
+      </c>
+      <c r="C45" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="D45" t="n">
+        <v>43</v>
+      </c>
+      <c r="E45" t="n">
+        <v>37</v>
+      </c>
+      <c r="F45" t="n">
+        <v>13124930</v>
+      </c>
+      <c r="G45" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>comex_ncm_27101922_fuel_oil_importacoes_kg</t>
+        </is>
+      </c>
+      <c r="B46" s="1" t="n">
+        <v>44196</v>
+      </c>
+      <c r="C46" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="D46" t="n">
+        <v>43</v>
+      </c>
+      <c r="E46" t="n">
+        <v>37</v>
+      </c>
+      <c r="F46" t="n">
+        <v>40054409</v>
+      </c>
+      <c r="G46" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>comex_ncm_47032900_celulose_nao_coniferas_exportacoes_fob_usd</t>
+        </is>
+      </c>
+      <c r="B47" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="C47" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D47" t="n">
+        <v>80</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" t="n">
+        <v>488810441</v>
+      </c>
+      <c r="G47" t="n">
+        <v>748163251</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>comex_ncm_47032900_celulose_nao_coniferas_exportacoes_kg</t>
+        </is>
+      </c>
+      <c r="B48" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="C48" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D48" t="n">
+        <v>80</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" t="n">
+        <v>1351894846</v>
+      </c>
+      <c r="G48" t="n">
+        <v>1412673002</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>comex_ncm_47032900_celulose_nao_coniferas_importacoes_fob_usd</t>
+        </is>
+      </c>
+      <c r="B49" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="C49" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D49" t="n">
+        <v>70</v>
+      </c>
+      <c r="E49" t="n">
+        <v>10</v>
+      </c>
+      <c r="F49" t="n">
+        <v>23393</v>
+      </c>
+      <c r="G49" t="n">
+        <v>1381516</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>comex_ncm_47032900_celulose_nao_coniferas_importacoes_kg</t>
+        </is>
+      </c>
+      <c r="B50" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="C50" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D50" t="n">
+        <v>70</v>
+      </c>
+      <c r="E50" t="n">
+        <v>10</v>
+      </c>
+      <c r="F50" t="n">
+        <v>40720</v>
+      </c>
+      <c r="G50" t="n">
+        <v>1452782</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/comexstat/resumo_disponibilidade_comexstat.xlsx
+++ b/data/final/comexstat/resumo_disponibilidade_comexstat.xlsx
@@ -685,7 +685,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>comex_ncm_02023000_carne_bovina_congelada_exportacoes_fob_usd</t>
+          <t>acucares_cana_exp_fob</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
@@ -701,16 +701,16 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>500185177</v>
+        <v>395907378</v>
       </c>
       <c r="G11" t="n">
-        <v>967242706</v>
+        <v>753147930</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>comex_ncm_02023000_carne_bovina_congelada_exportacoes_kg</t>
+          <t>acucares_cana_exp_kg</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
@@ -726,16 +726,16 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>103909023</v>
+        <v>1403790404</v>
       </c>
       <c r="G12" t="n">
-        <v>162300453</v>
+        <v>2221291720</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>comex_ncm_02023000_carne_bovina_congelada_importacoes_fob_usd</t>
+          <t>acucares_cana_imp_fob</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
@@ -745,22 +745,22 @@
         <v>46265</v>
       </c>
       <c r="D13" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>9788257</v>
+        <v>42579</v>
       </c>
       <c r="G13" t="n">
-        <v>9868969</v>
+        <v>170442</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>comex_ncm_02023000_carne_bovina_congelada_importacoes_kg</t>
+          <t>acucares_cana_imp_kg</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
@@ -770,22 +770,22 @@
         <v>46265</v>
       </c>
       <c r="D14" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>1182973</v>
+        <v>41657</v>
       </c>
       <c r="G14" t="n">
-        <v>942383</v>
+        <v>143344</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>comex_ncm_09011110_cafe_nao_torrado_exportacoes_fob_usd</t>
+          <t>cafe_nao_torrado_exp_fob</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
@@ -810,7 +810,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>comex_ncm_09011110_cafe_nao_torrado_exportacoes_kg</t>
+          <t>cafe_nao_torrado_exp_kg</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
@@ -835,7 +835,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>comex_ncm_09011110_cafe_nao_torrado_importacoes_fob_usd</t>
+          <t>cafe_nao_torrado_imp_fob</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
@@ -860,7 +860,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>comex_ncm_09011110_cafe_nao_torrado_importacoes_kg</t>
+          <t>cafe_nao_torrado_imp_kg</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
@@ -885,7 +885,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>comex_ncm_10059010_milho_em_grao_exportacoes_fob_usd</t>
+          <t>carne_bovina_congelada_exp_fob</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
@@ -901,16 +901,16 @@
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>349915062</v>
+        <v>500185177</v>
       </c>
       <c r="G19" t="n">
-        <v>1002656682</v>
+        <v>967242706</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>comex_ncm_10059010_milho_em_grao_exportacoes_kg</t>
+          <t>carne_bovina_congelada_exp_kg</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
@@ -926,16 +926,16 @@
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>2083530104</v>
+        <v>103909023</v>
       </c>
       <c r="G20" t="n">
-        <v>4653100189</v>
+        <v>162300453</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>comex_ncm_10059010_milho_em_grao_importacoes_fob_usd</t>
+          <t>carne_bovina_congelada_imp_fob</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
@@ -951,16 +951,16 @@
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>26216991</v>
+        <v>9788257</v>
       </c>
       <c r="G21" t="n">
-        <v>33273820</v>
+        <v>9868969</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>comex_ncm_10059010_milho_em_grao_importacoes_kg</t>
+          <t>carne_bovina_congelada_imp_kg</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
@@ -976,16 +976,16 @@
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>196178640</v>
+        <v>1182973</v>
       </c>
       <c r="G22" t="n">
-        <v>199281400</v>
+        <v>942383</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>comex_ncm_12019000_soja_exceto_semeadura_exportacoes_fob_usd</t>
+          <t>celulose_nao_coniferas_exp_fob</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
@@ -1001,16 +1001,16 @@
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>504774218</v>
+        <v>488810441</v>
       </c>
       <c r="G23" t="n">
-        <v>4410039153</v>
+        <v>748163251</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>comex_ncm_12019000_soja_exceto_semeadura_exportacoes_kg</t>
+          <t>celulose_nao_coniferas_exp_kg</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
@@ -1026,16 +1026,16 @@
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>1397018249</v>
+        <v>1351894846</v>
       </c>
       <c r="G24" t="n">
-        <v>9808807495</v>
+        <v>1412673002</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>comex_ncm_12019000_soja_exceto_semeadura_importacoes_fob_usd</t>
+          <t>celulose_nao_coniferas_imp_fob</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
@@ -1045,22 +1045,22 @@
         <v>46265</v>
       </c>
       <c r="D25" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="E25" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F25" t="n">
-        <v>6305340</v>
+        <v>23393</v>
       </c>
       <c r="G25" t="n">
-        <v>44621019</v>
+        <v>1381516</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>comex_ncm_12019000_soja_exceto_semeadura_importacoes_kg</t>
+          <t>celulose_nao_coniferas_imp_kg</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
@@ -1070,22 +1070,22 @@
         <v>46265</v>
       </c>
       <c r="D26" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="E26" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F26" t="n">
-        <v>19690000</v>
+        <v>40720</v>
       </c>
       <c r="G26" t="n">
-        <v>109088024</v>
+        <v>1452782</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>comex_ncm_17011400_acucares_cana_exportacoes_fob_usd</t>
+          <t>fuel_oil_exp_fob</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
@@ -1101,16 +1101,16 @@
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>395907378</v>
+        <v>401663716</v>
       </c>
       <c r="G27" t="n">
-        <v>753147930</v>
+        <v>893582419</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>comex_ncm_17011400_acucares_cana_exportacoes_kg</t>
+          <t>fuel_oil_exp_kg</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
@@ -1126,66 +1126,66 @@
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>1403790404</v>
+        <v>955961547</v>
       </c>
       <c r="G28" t="n">
-        <v>2221291720</v>
+        <v>1438094595</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>comex_ncm_17011400_acucares_cana_importacoes_fob_usd</t>
+          <t>fuel_oil_imp_fob</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
-        <v>43861</v>
+        <v>44196</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D29" t="n">
-        <v>79</v>
+        <v>43</v>
       </c>
       <c r="E29" t="n">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="F29" t="n">
-        <v>42579</v>
+        <v>13124930</v>
       </c>
       <c r="G29" t="n">
-        <v>170442</v>
+        <v>60</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>comex_ncm_17011400_acucares_cana_importacoes_kg</t>
+          <t>fuel_oil_imp_kg</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
-        <v>43861</v>
+        <v>44196</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D30" t="n">
-        <v>79</v>
+        <v>43</v>
       </c>
       <c r="E30" t="n">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="F30" t="n">
-        <v>41657</v>
+        <v>40054409</v>
       </c>
       <c r="G30" t="n">
-        <v>143344</v>
+        <v>24</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>comex_ncm_23040090_residuos_oleo_soja_exportacoes_fob_usd</t>
+          <t>milho_em_grao_exp_fob</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
@@ -1201,16 +1201,16 @@
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>281324952</v>
+        <v>349915062</v>
       </c>
       <c r="G31" t="n">
-        <v>646488066</v>
+        <v>1002656682</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>comex_ncm_23040090_residuos_oleo_soja_exportacoes_kg</t>
+          <t>milho_em_grao_exp_kg</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
@@ -1226,66 +1226,66 @@
         <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>831821378</v>
+        <v>2083530104</v>
       </c>
       <c r="G32" t="n">
-        <v>1790486389</v>
+        <v>4653100189</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>comex_ncm_23040090_residuos_oleo_soja_importacoes_fob_usd</t>
+          <t>milho_em_grao_imp_fob</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
-        <v>43890</v>
+        <v>43861</v>
       </c>
       <c r="C33" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D33" t="n">
-        <v>5</v>
+        <v>80</v>
       </c>
       <c r="E33" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>2282</v>
+        <v>26216991</v>
       </c>
       <c r="G33" t="n">
-        <v>360</v>
+        <v>33273820</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>comex_ncm_23040090_residuos_oleo_soja_importacoes_kg</t>
+          <t>milho_em_grao_imp_kg</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
-        <v>43890</v>
+        <v>43861</v>
       </c>
       <c r="C34" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D34" t="n">
-        <v>5</v>
+        <v>80</v>
       </c>
       <c r="E34" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>2500</v>
+        <v>196178640</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>199281400</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>comex_ncm_26011100_minerio_ferro_nao_aglomerado_exportacoes_fob_usd</t>
+          <t>minerio_ferro_nao_aglomerado_exp_fob</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
@@ -1310,7 +1310,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>comex_ncm_26011100_minerio_ferro_nao_aglomerado_exportacoes_kg</t>
+          <t>minerio_ferro_nao_aglomerado_exp_kg</t>
         </is>
       </c>
       <c r="B36" s="1" t="n">
@@ -1335,7 +1335,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>comex_ncm_26011100_minerio_ferro_nao_aglomerado_importacoes_fob_usd</t>
+          <t>minerio_ferro_nao_aglomerado_imp_fob</t>
         </is>
       </c>
       <c r="B37" s="1" t="n">
@@ -1360,7 +1360,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>comex_ncm_26011100_minerio_ferro_nao_aglomerado_importacoes_kg</t>
+          <t>minerio_ferro_nao_aglomerado_imp_kg</t>
         </is>
       </c>
       <c r="B38" s="1" t="n">
@@ -1385,7 +1385,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>comex_ncm_27090010_oleos_brutos_petroleo_exportacoes_fob_usd</t>
+          <t>oleos_brutos_petroleo_exp_fob</t>
         </is>
       </c>
       <c r="B39" s="1" t="n">
@@ -1410,7 +1410,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>comex_ncm_27090010_oleos_brutos_petroleo_exportacoes_kg</t>
+          <t>oleos_brutos_petroleo_exp_kg</t>
         </is>
       </c>
       <c r="B40" s="1" t="n">
@@ -1435,7 +1435,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>comex_ncm_27090010_oleos_brutos_petroleo_importacoes_fob_usd</t>
+          <t>oleos_brutos_petroleo_imp_fob</t>
         </is>
       </c>
       <c r="B41" s="1" t="n">
@@ -1460,7 +1460,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>comex_ncm_27090010_oleos_brutos_petroleo_importacoes_kg</t>
+          <t>oleos_brutos_petroleo_imp_kg</t>
         </is>
       </c>
       <c r="B42" s="1" t="n">
@@ -1485,7 +1485,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>comex_ncm_27101922_fuel_oil_exportacoes_fob_usd</t>
+          <t>residuos_oleo_soja_exp_fob</t>
         </is>
       </c>
       <c r="B43" s="1" t="n">
@@ -1501,16 +1501,16 @@
         <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>401663716</v>
+        <v>281324952</v>
       </c>
       <c r="G43" t="n">
-        <v>893582419</v>
+        <v>646488066</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>comex_ncm_27101922_fuel_oil_exportacoes_kg</t>
+          <t>residuos_oleo_soja_exp_kg</t>
         </is>
       </c>
       <c r="B44" s="1" t="n">
@@ -1526,66 +1526,66 @@
         <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>955961547</v>
+        <v>831821378</v>
       </c>
       <c r="G44" t="n">
-        <v>1438094595</v>
+        <v>1790486389</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>comex_ncm_27101922_fuel_oil_importacoes_fob_usd</t>
+          <t>residuos_oleo_soja_imp_fob</t>
         </is>
       </c>
       <c r="B45" s="1" t="n">
-        <v>44196</v>
+        <v>43890</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D45" t="n">
-        <v>43</v>
+        <v>5</v>
       </c>
       <c r="E45" t="n">
-        <v>37</v>
+        <v>75</v>
       </c>
       <c r="F45" t="n">
-        <v>13124930</v>
+        <v>2282</v>
       </c>
       <c r="G45" t="n">
-        <v>60</v>
+        <v>360</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>comex_ncm_27101922_fuel_oil_importacoes_kg</t>
+          <t>residuos_oleo_soja_imp_kg</t>
         </is>
       </c>
       <c r="B46" s="1" t="n">
-        <v>44196</v>
+        <v>43890</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D46" t="n">
-        <v>43</v>
+        <v>5</v>
       </c>
       <c r="E46" t="n">
-        <v>37</v>
+        <v>75</v>
       </c>
       <c r="F46" t="n">
-        <v>40054409</v>
+        <v>2500</v>
       </c>
       <c r="G46" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>comex_ncm_47032900_celulose_nao_coniferas_exportacoes_fob_usd</t>
+          <t>soja_exceto_semeadura_exp_fob</t>
         </is>
       </c>
       <c r="B47" s="1" t="n">
@@ -1601,16 +1601,16 @@
         <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>488810441</v>
+        <v>504774218</v>
       </c>
       <c r="G47" t="n">
-        <v>748163251</v>
+        <v>4410039153</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>comex_ncm_47032900_celulose_nao_coniferas_exportacoes_kg</t>
+          <t>soja_exceto_semeadura_exp_kg</t>
         </is>
       </c>
       <c r="B48" s="1" t="n">
@@ -1626,16 +1626,16 @@
         <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>1351894846</v>
+        <v>1397018249</v>
       </c>
       <c r="G48" t="n">
-        <v>1412673002</v>
+        <v>9808807495</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>comex_ncm_47032900_celulose_nao_coniferas_importacoes_fob_usd</t>
+          <t>soja_exceto_semeadura_imp_fob</t>
         </is>
       </c>
       <c r="B49" s="1" t="n">
@@ -1645,22 +1645,22 @@
         <v>46265</v>
       </c>
       <c r="D49" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="E49" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F49" t="n">
-        <v>23393</v>
+        <v>6305340</v>
       </c>
       <c r="G49" t="n">
-        <v>1381516</v>
+        <v>44621019</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>comex_ncm_47032900_celulose_nao_coniferas_importacoes_kg</t>
+          <t>soja_exceto_semeadura_imp_kg</t>
         </is>
       </c>
       <c r="B50" s="1" t="n">
@@ -1670,16 +1670,16 @@
         <v>46265</v>
       </c>
       <c r="D50" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="E50" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F50" t="n">
-        <v>40720</v>
+        <v>19690000</v>
       </c>
       <c r="G50" t="n">
-        <v>1452782</v>
+        <v>109088024</v>
       </c>
     </row>
   </sheetData>
